--- a/backend/data/account_import_template.xlsx
+++ b/backend/data/account_import_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17680" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="账户数据中心模板" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="字段说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="示例数据" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="账户数据中心模板" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="示例数据" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -10305,7 +10305,7 @@
       <c r="V6" s="3" t="n"/>
       <c r="W6" s="3" t="n"/>
     </row>
-    <row r="7" ht="28" customHeight="1" s="18">
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>银行账号</t>
@@ -10354,10 +10354,10 @@
       <c r="V7" s="3" t="n"/>
       <c r="W7" s="3" t="n"/>
     </row>
-    <row r="8" ht="42" customHeight="1" s="18">
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>开户行名称</t>
+          <t>账户名称</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -10403,7 +10403,7 @@
       <c r="V8" s="3" t="n"/>
       <c r="W8" s="3" t="n"/>
     </row>
-    <row r="9" ht="28.5" customHeight="1" s="18">
+    <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>账户编号</t>
@@ -10499,7 +10499,7 @@
       <c r="V10" s="3" t="n"/>
       <c r="W10" s="3" t="n"/>
     </row>
-    <row r="11" ht="70" customHeight="1" s="18">
+    <row r="11" ht="28" customHeight="1" s="18">
       <c r="A11" s="1" t="inlineStr">
         <is>
           <t>账户类型</t>
@@ -10646,7 +10646,7 @@
       <c r="V13" s="3" t="n"/>
       <c r="W13" s="3" t="n"/>
     </row>
-    <row r="14" ht="42" customHeight="1" s="18">
+    <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
           <t>录入方式</t>
@@ -10695,7 +10695,7 @@
       <c r="V14" s="3" t="n"/>
       <c r="W14" s="3" t="n"/>
     </row>
-    <row r="15" ht="28" customHeight="1" s="18">
+    <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
           <t>币种</t>
@@ -10877,7 +10877,7 @@
       <c r="V18" s="3" t="n"/>
       <c r="W18" s="3" t="n"/>
     </row>
-    <row r="19" ht="42.5" customHeight="1" s="18">
+    <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
           <t>是否允许手工录入</t>
@@ -10926,7 +10926,7 @@
       <c r="V19" s="3" t="n"/>
       <c r="W19" s="3" t="n"/>
     </row>
-    <row r="20" ht="29" customHeight="1" s="18">
+    <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
           <t>状态</t>
@@ -10975,7 +10975,7 @@
       <c r="V20" s="3" t="n"/>
       <c r="W20" s="3" t="n"/>
     </row>
-    <row r="21" ht="28" customHeight="1" s="18">
+    <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
           <t>备注</t>
